--- a/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas. Il dit : c'est notre secret. Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a peur. Cédric marche vers papa. Il prend sa main. Cédric dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute. Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
+          <t>Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas. C'est notre secret. Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a peur. Cédric marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute. Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas.
+narrateur|C'est notre secret.
+narrateur|Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a peur. Cédric marche vers papa. Il prend sa main.
+enfant-m|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
+papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute.
+narrateur|Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric a peur. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric a senti le malaise. Il a marché vers papa. Il a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Cédric a peur. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,7 @@
           <t>narrateur|Cédric a senti le malaise. Il a marché vers papa. Il a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1852,7 @@
           <t>narrateur|Cédric s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cédric raconte ce qui fait peur</t>
+          <t>Raphaël raconte au parc</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une coccinelle marche sur un genou. Raphaël raconte au parc, puis encore à la maison.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas. C'est notre secret. Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a peur. Cédric marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute. Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
+          <t>Une coccinelle marche sur un genou. Elle est rouge à points noirs. La chaîne de la balançoire chante. Un pissenlit garde son duvet. L'herbe du parc est tiède. Elle sent le soleil. Un caillou blanc brille près du pied. Raphaël, la coccinelle te visite. Elle chatouille un peu. Elle est toute légère. En ce moment, Raphaël est au parc. Il est assis dans l'herbe. La coccinelle s'envole. Elle est partie, papa. Oui. On reste dans l'herbe. Une voix d'adulte parle tout bas. Raphaël sent son ventre. Le ventre est serré. C'est un malaise. Raphaël a peur. Il se lève. Il marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On va le dire à maman ? Oui, Raphaël. Bravo. Tu as fait du bon travail. La chaîne de la balançoire se tait. Le caillou blanc reste dans l'herbe. Plus tard, ils rentrent à la maison. Le paillasson est un peu rêche. Maman plie un linge chaud. Le linge sent le soleil. Raphaël a quelque chose à dire. Raphaël marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Même ici, à la maison. Je me sens plus léger. Bravo, Raphaël. Tu as fait du bon travail. Au parc, puis ici. On va raconter à papa ou maman. Raphaël s'assoit près de maman. Le linge chaud touche son bras. Papa s'assoit aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas.
-narrateur|C'est notre secret.
-narrateur|Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a peur. Cédric marche vers papa. Il prend sa main.
-enfant-m|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
-papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute.
-narrateur|Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.</t>
+          <t>narrateur|Une coccinelle marche sur un genou.
+narrateur|Elle est rouge à points noirs.
+narrateur|La chaîne de la balançoire chante.
+narrateur|Un pissenlit garde son duvet.
+narrateur|L'herbe du parc est tiède.
+narrateur|Elle sent le soleil.
+narrateur|Un caillou blanc brille près du pied.
+papa|Raphaël, la coccinelle te visite.
+enfant-m|Elle chatouille un peu.
+papa|Elle est toute légère.
+narrateur|En ce moment, Raphaël est au parc.
+narrateur|Il est assis dans l'herbe.
+narrateur|La coccinelle s'envole.
+enfant-m|Elle est partie, papa.
+papa|Oui.
+papa|On reste dans l'herbe.
+narrateur|Une voix d'adulte parle tout bas.
+narrateur|Raphaël sent son ventre.
+narrateur|Le ventre est serré.
+narrateur|C'est un malaise.
+narrateur|Raphaël a peur.
+narrateur|Il se lève.
+narrateur|Il marche vers papa.
+narrateur|Il prend sa main.
+enfant-m|Papa, un adulte a parlé d'un secret.
+enfant-m|Mon ventre est serré.
+enfant-m|J'ai peur.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+papa|Je reste tout près.
+enfant-m|On va le dire à maman ?
+papa|Oui, Raphaël.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|Le caillou blanc reste dans l'herbe.
+narrateur|Plus tard, ils rentrent à la maison.
+narrateur|Le paillasson est un peu rêche.
+narrateur|Maman plie un linge chaud.
+maman|Le linge sent le soleil.
+papa|Raphaël a quelque chose à dire.
+narrateur|Raphaël marche vers maman.
+enfant-m|Maman, j'ai eu peur au parc.
+enfant-m|Mon ventre était serré.
+enfant-m|J'ai raconté à papa.
+maman|Merci de raconter.
+maman|Tu as le droit de le dire.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+maman|Même ici, à la maison.
+enfant-m|Je me sens plus léger.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Au parc, puis ici.
+papa|On va raconter à papa ou maman.
+narrateur|Raphaël s'assoit près de maman.
+narrateur|Le linge chaud touche son bras.
+narrateur|Papa s'assoit aussi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cédric a peur. Que fait-il ?</t>
+          <t>Raphaël a peur. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Cédric a peur. Que fait-il ?</t>
+          <t>narrateur|Raphaël a peur.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1537,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cédric a senti le malaise. Il a marché vers papa. Il a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>Raphaël a senti le malaise. Il a marché vers papa. Il a raconté. Tu as raconté au parc ? Oui. Puis à la maison aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. La coccinelle n'est plus sur le genou. Le linge reste chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1681,7 +1748,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cédric a senti le malaise. Il a marché vers papa. Il a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Raphaël a senti le malaise.
+narrateur|Il a marché vers papa.
+narrateur|Il a raconté.
+papa|Tu as raconté au parc ?
+enfant-m|Oui.
+maman|Puis à la maison aussi.
+maman|Bravo.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+narrateur|La coccinelle n'est plus sur le genou.
+narrateur|Le linge reste chaud.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1709,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cédric s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>Raphaël s'assoit près de maman. Papa pose le caillou blanc. Il vient du parc. Tu es là, avec nous. Oui. Le linge est chaud. Tu as raconté. C'est du bon travail. Je suis près de toi. Le paillasson garde un brin d'herbe. On reste encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,7 +1926,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cédric s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Raphaël s'assoit près de maman.
+narrateur|Papa pose le caillou blanc.
+maman|Il vient du parc.
+papa|Tu es là, avec nous.
+enfant-m|Oui.
+enfant-m|Le linge est chaud.
+maman|Tu as raconté.
+maman|C'est du bon travail.
+papa|Je suis près de toi.
+narrateur|Le paillasson garde un brin d'herbe.
+maman|On reste encore un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1877,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le caillou blanc dort sur la table. J'ai raconté. Bravo, Raphaël. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,7 +2104,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le caillou blanc dort sur la table.
+enfant-m|J'ai raconté.
+papa|Bravo, Raphaël.
+maman|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une coccinelle marche sur un genou. Elle est rouge à points noirs. La chaîne de la balançoire chante. Un pissenlit garde son duvet. L'herbe du parc est tiède. Elle sent le soleil. Un caillou blanc brille près du pied. Raphaël, la coccinelle te visite. Elle chatouille un peu. Elle est toute légère. En ce moment, Raphaël est au parc. Il est assis dans l'herbe. La coccinelle s'envole. Elle est partie, papa. Oui. On reste dans l'herbe. Une voix d'adulte parle tout bas. Raphaël sent son ventre. Le ventre est serré. C'est un malaise. Raphaël a peur. Il se lève. Il marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On va le dire à maman ? Oui, Raphaël. Bravo. Tu as fait du bon travail. La chaîne de la balançoire se tait. Le caillou blanc reste dans l'herbe. Plus tard, ils rentrent à la maison. Le paillasson est un peu rêche. Maman plie un linge chaud. Le linge sent le soleil. Raphaël a quelque chose à dire. Raphaël marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Même ici, à la maison. Je me sens plus léger. Bravo, Raphaël. Tu as fait du bon travail. Au parc, puis ici. On va raconter à papa ou maman. Raphaël s'assoit près de maman. Le linge chaud touche son bras. Papa s'assoit aussi.</t>
+          <t>Une coccinelle marche sur un genou. Elle est rouge à points noirs. La chaîne de la balançoire chante. Un pissenlit garde son duvet. L'herbe du parc est tiède. Elle sent le soleil. Un caillou blanc brille près du pied. Raphaël, la coccinelle te visite. Elle chatouille un peu. Elle est toute légère. En ce moment, Raphaël est au parc. Il est assis dans l'herbe. La coccinelle s'envole. Elle est partie, papa. Oui. On reste dans l'herbe. Une voix d'adulte parle tout bas. Raphaël sent son ventre. Le ventre est serré. C'est un malaise. Raphaël a peur. Il se lève. Il marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On va le dire à maman ? Oui, Raphaël. Bravo. La chaîne de la balançoire se tait. Le caillou blanc reste dans l'herbe. Plus tard, ils rentrent à la maison. Le paillasson est un peu rêche. Maman plie un linge chaud. Le linge sent le soleil. Raphaël a quelque chose à dire. Raphaël marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Même ici, à la maison. Je me sens plus léger. Bravo, Raphaël. Au parc, puis ici. On va raconter à papa ou maman. Raphaël s'assoit près de maman. Le linge chaud touche son bras. Papa s'assoit aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cédric est au parc avec papa. Il sent l'herbe. Un adulte parle tout bas. Il dit : c'est notre secret. Cédric sent son ventre. C'est serré. C'est un malaise. Cédric a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Cédric marche vers papa. Il prend sa main. Cédric dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cédric le dit aussi à maman. Maman écoute. Cédric se sent plus léger. Même leçon, autre lieu. Peur ou malaise, on raconte à papa ou maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une coccinelle marche sur un genou. Elle est rouge à points noirs. La chaîne de la balançoire chante. Un pissenlit garde son duvet. L'herbe du parc est tiède. Elle sent le soleil. Un caillou blanc brille près du pied. Raphaël, la coccinelle te visite. Elle chatouille un peu. Elle est toute légère. En ce moment, Raphaël est au parc. Il est assis dans l'herbe. La coccinelle s'envole. Elle est partie, papa. Oui. On reste dans l'herbe. Une voix d'adulte parle tout bas. Raphaël sent son ventre. Le ventre est serré. C'est un malaise. Raphaël a peur. Il se lève. Il marche vers papa. Il prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On va le dire à maman ? Oui, Raphaël. Bravo. La chaîne de la balançoire se tait. Le caillou blanc reste dans l'herbe. Plus tard, ils rentrent à la maison. Le paillasson est un peu rêche. Maman plie un linge chaud. Le linge sent le soleil. Raphaël a quelque chose à dire. Raphaël marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Même ici, à la maison. Je me sens plus léger. Bravo, Raphaël. Au parc, puis ici. On va raconter à papa ou maman. Raphaël s'assoit près de maman. Le linge chaud touche son bras. Papa s'assoit aussi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 enfant-m|On va le dire à maman ?
 papa|Oui, Raphaël.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|La chaîne de la balançoire se tait.
 narrateur|Le caillou blanc reste dans l'herbe.
 narrateur|Plus tard, ils rentrent à la maison.
@@ -1378,7 +1377,6 @@
 maman|Même ici, à la maison.
 enfant-m|Je me sens plus léger.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
 papa|Au parc, puis ici.
 papa|On va raconter à papa ou maman.
 narrateur|Raphaël s'assoit près de maman.
@@ -1420,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cédric a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a peur. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1577,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1609,7 +1606,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cédric a senti le malaise. Il a marché vers papa. Il a raconté. Papa et maman écoutent. Ce qui fait &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt; se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a senti le malaise. Il a marché vers papa. Il a raconté. Tu as raconté au parc ? Oui. Puis à la maison aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. La coccinelle n'est plus sur le genou. Le linge reste chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1758,6 @@
 narrateur|Le linge reste chaud.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'assoit près de maman. Papa pose le caillou blanc. Il vient du parc. Tu es là, avec nous. Oui. Le linge est chaud. Tu as raconté. C'est du bon travail. Je suis près de toi. Le paillasson garde un brin d'herbe. On reste encore un peu.</t>
+          <t>Raphaël s'assoit près de maman. Papa pose le caillou blanc. Il vient du parc. Tu es là, avec nous. Oui. Le linge est chaud. Tu as raconté. Je suis près de toi. Le paillasson garde un brin d'herbe. On reste encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cédric s'assoit près de maman. Papa est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël s'assoit près de maman. Papa pose le caillou blanc. Il vient du parc. Tu es là, avec nous. Oui. Le linge est chaud. Tu as raconté. Je suis près de toi. Le paillasson garde un brin d'herbe. On reste encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,13 +1929,11 @@
 enfant-m|Oui.
 enfant-m|Le linge est chaud.
 maman|Tu as raconté.
-maman|C'est du bon travail.
 papa|Je suis près de toi.
 narrateur|Le paillasson garde un brin d'herbe.
 maman|On reste encore un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc dort sur la table. J'ai raconté. Bravo, Raphaël. On t'écoute. L'histoire est finie.</t>
+          <t>Le caillou blanc dort sur la table. J'ai raconté. Bravo, Raphaël. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le caillou blanc dort sur la table. J'ai raconté. Bravo, Raphaël. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,11 +2101,9 @@
           <t>narrateur|Le caillou blanc dort sur la table.
 enfant-m|J'ai raconté.
 papa|Bravo, Raphaël.
-maman|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cédric, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
